--- a/marketing/trackers/kpi-tableau-de-bord.xlsx
+++ b/marketing/trackers/kpi-tableau-de-bord.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="123">
   <si>
     <t xml:space="preserve">Nhill — tableau de bord commercial (90 jours) / sales dashboard</t>
   </si>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">démos / contacts</t>
   </si>
   <si>
-    <t xml:space="preserve">Pilotes signés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conventions signées</t>
+    <t xml:space="preserve">Essais acceptés (pilotes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conditions de l'essai acceptées par écrit</t>
   </si>
   <si>
     <t xml:space="preserve">Taux démo → pilote</t>
   </si>
   <si>
-    <t xml:space="preserve">pilotes signés / démos</t>
+    <t xml:space="preserve">essais acceptés / démos</t>
   </si>
   <si>
     <t xml:space="preserve">Pilotes actifs (dernière semaine saisie)</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">Démos faites / done</t>
   </si>
   <si>
-    <t xml:space="preserve">Pilotes signés / signed</t>
+    <t xml:space="preserve">Essais acceptés / trials accepted</t>
   </si>
   <si>
     <t xml:space="preserve">Pilotes actifs / active</t>
@@ -407,48 +407,6 @@
     <t xml:space="preserve">notes</t>
   </si>
   <si>
-    <t xml:space="preserve">P-0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXEMPLE — Boutique fictive (démo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">détail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exemple Nom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propriétaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">terrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">démo fixée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">démonstration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ligne d'exemple à supprimer</t>
-  </si>
-  <si>
     <t xml:space="preserve">nom / name</t>
   </si>
   <si>
@@ -480,24 +438,6 @@
   </si>
   <si>
     <t xml:space="preserve">derniere_rencontre / last_meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXEMPLE — Partenaire fictif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intégrateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gombe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-24</t>
   </si>
 </sst>
 </file>
@@ -515,7 +455,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0000"/>
     <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -607,14 +547,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -685,7 +617,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -791,10 +723,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2324,7 +2252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2404,62 +2332,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27" t="s">
-        <v>125</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N1002" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N1001" type="list">
       <formula1>"identifié,contacté,démo fixée,démo faite,pilote proposé,pilote en cours,proposition,client,perdu,plus tard"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2479,7 +2354,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -2499,87 +2374,43 @@
         <v>93</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
